--- a/DocDesign/RandomTool/Game.25/excel/FruitSlotsFeature.xlsx
+++ b/DocDesign/RandomTool/Game.25/excel/FruitSlotsFeature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\DocDesign\RandomTool\Game.25\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69DA6FE-D66B-4DDA-B79D-C4FB0A77498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8DC9C0-56E3-4808-A952-9CCC903E80A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32160" yWindow="2940" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FruitSlotsFeature" sheetId="1" r:id="rId1"/>
@@ -1183,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="4">
-        <v>0.01</v>
+        <v>4.9599999999999998E-2</v>
       </c>
       <c r="C6" s="4">
         <v>0.02</v>
